--- a/InputData/fuels/MPIiFE/Max Perc Inc in Fuel Exports.xlsx
+++ b/InputData/fuels/MPIiFE/Max Perc Inc in Fuel Exports.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28906"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250505_Last30/Topes/MPIiFE/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{61302665-8610-FD45-8B58-7B652B53A024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDABABF-7455-4E23-A5F2-6FAFC8A60D57}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28180" windowHeight="12520" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="MPIiFE" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -33,10 +45,69 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>none needed for U.S.</t>
+    <t>none needed for MX</t>
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>This variable allows you to specify a cap on how much fuel exports</t>
+  </si>
+  <si>
+    <t>may increase in response to policies.</t>
+  </si>
+  <si>
+    <t>This can reflect physical constraints on exports, such as limited</t>
+  </si>
+  <si>
+    <t>export terminal or trans-border pipeline capacity.</t>
+  </si>
+  <si>
+    <t>Alternatively, it may represent a legislative cap on exports.</t>
+  </si>
+  <si>
+    <t>Note that even if this cap is high, fuel exports will not increase</t>
+  </si>
+  <si>
+    <t>in response to a policy package unless allowed to do so in</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">variable </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fuels/PoFDCtAE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>For MX, we do not wish to impose a cap,</t>
+  </si>
+  <si>
+    <t>changes in exports using fuels/PoFDCtAE), so we pick</t>
+  </si>
+  <si>
+    <t>an arbitrarily high percentage.</t>
+  </si>
+  <si>
+    <t>Max Percentage Increase (dimensionless)</t>
   </si>
   <si>
     <t>electricity (not used in this variable)</t>
@@ -101,71 +172,12 @@
   <si>
     <t>hydrogen</t>
   </si>
-  <si>
-    <t>Max Percentage Increase (dimensionless)</t>
-  </si>
-  <si>
-    <t>This variable allows you to specify a cap on how much fuel exports</t>
-  </si>
-  <si>
-    <t>may increase in response to policies.</t>
-  </si>
-  <si>
-    <t>This can reflect physical constraints on exports, such as limited</t>
-  </si>
-  <si>
-    <t>export terminal or trans-border pipeline capacity.</t>
-  </si>
-  <si>
-    <t>Note that even if this cap is high, fuel exports will not increase</t>
-  </si>
-  <si>
-    <t>in response to a policy package unless allowed to do so in</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">variable </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>fuels/PoFDCtAE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>For the U.S., we do not wish to impose a cap (we limit</t>
-  </si>
-  <si>
-    <t>changes in exports using fuels/PoFDCtAE), so we pick</t>
-  </si>
-  <si>
-    <t>an arbitrarily high percentage.</t>
-  </si>
-  <si>
-    <t>Alternatively, it may represent a legislative cap on exports.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,20 +220,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -503,16 +512,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -520,64 +529,64 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -587,233 +596,353 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BC22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" ht="15.95">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1">
         <v>2018</v>
       </c>
       <c r="D1" s="3">
         <v>2019</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1">
         <v>2020</v>
       </c>
       <c r="F1" s="3">
         <v>2021</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1">
         <v>2022</v>
       </c>
       <c r="H1" s="3">
         <v>2023</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1">
         <v>2024</v>
       </c>
       <c r="J1" s="3">
         <v>2025</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1">
         <v>2026</v>
       </c>
       <c r="L1" s="3">
         <v>2027</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1">
         <v>2028</v>
       </c>
       <c r="N1" s="3">
         <v>2029</v>
       </c>
-      <c r="O1" s="4">
+      <c r="O1">
         <v>2030</v>
       </c>
       <c r="P1" s="3">
         <v>2031</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="Q1">
         <v>2032</v>
       </c>
       <c r="R1" s="3">
         <v>2033</v>
       </c>
-      <c r="S1" s="4">
+      <c r="S1">
         <v>2034</v>
       </c>
       <c r="T1" s="3">
         <v>2035</v>
       </c>
-      <c r="U1" s="4">
+      <c r="U1">
         <v>2036</v>
       </c>
       <c r="V1" s="3">
         <v>2037</v>
       </c>
-      <c r="W1" s="4">
+      <c r="W1">
         <v>2038</v>
       </c>
       <c r="X1" s="3">
         <v>2039</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Y1">
         <v>2040</v>
       </c>
       <c r="Z1" s="3">
         <v>2041</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AA1">
         <v>2042</v>
       </c>
       <c r="AB1" s="3">
         <v>2043</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AC1">
         <v>2044</v>
       </c>
       <c r="AD1" s="3">
         <v>2045</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AE1">
         <v>2046</v>
       </c>
       <c r="AF1" s="3">
         <v>2047</v>
       </c>
-      <c r="AG1" s="4">
+      <c r="AG1">
         <v>2048</v>
       </c>
       <c r="AH1" s="3">
         <v>2049</v>
       </c>
-      <c r="AI1" s="4">
+      <c r="AI1">
         <v>2050</v>
       </c>
+      <c r="AJ1" s="3">
+        <v>2051</v>
+      </c>
+      <c r="AK1">
+        <v>2052</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>2053</v>
+      </c>
+      <c r="AM1">
+        <v>2054</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>2055</v>
+      </c>
+      <c r="AO1">
+        <v>2056</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>2057</v>
+      </c>
+      <c r="AQ1">
+        <v>2058</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>2059</v>
+      </c>
+      <c r="AS1">
+        <v>2060</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>2061</v>
+      </c>
+      <c r="AU1">
+        <v>2062</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>2063</v>
+      </c>
+      <c r="AW1">
+        <v>2064</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>2065</v>
+      </c>
+      <c r="AY1">
+        <v>2066</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>2067</v>
+      </c>
+      <c r="BA1">
+        <v>2068</v>
+      </c>
+      <c r="BB1" s="3">
+        <v>2069</v>
+      </c>
+      <c r="BC1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="6">
+    <row r="2" spans="1:55" ht="15.95">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
+    <row r="3" spans="1:55">
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -917,10 +1046,70 @@
       <c r="AI3">
         <v>999</v>
       </c>
+      <c r="AJ3">
+        <v>999</v>
+      </c>
+      <c r="AK3">
+        <v>999</v>
+      </c>
+      <c r="AL3">
+        <v>999</v>
+      </c>
+      <c r="AM3">
+        <v>999</v>
+      </c>
+      <c r="AN3">
+        <v>999</v>
+      </c>
+      <c r="AO3">
+        <v>999</v>
+      </c>
+      <c r="AP3">
+        <v>999</v>
+      </c>
+      <c r="AQ3">
+        <v>999</v>
+      </c>
+      <c r="AR3">
+        <v>999</v>
+      </c>
+      <c r="AS3">
+        <v>999</v>
+      </c>
+      <c r="AT3">
+        <v>999</v>
+      </c>
+      <c r="AU3">
+        <v>999</v>
+      </c>
+      <c r="AV3">
+        <v>999</v>
+      </c>
+      <c r="AW3">
+        <v>999</v>
+      </c>
+      <c r="AX3">
+        <v>999</v>
+      </c>
+      <c r="AY3">
+        <v>999</v>
+      </c>
+      <c r="AZ3">
+        <v>999</v>
+      </c>
+      <c r="BA3">
+        <v>999</v>
+      </c>
+      <c r="BB3">
+        <v>999</v>
+      </c>
+      <c r="BC3">
+        <v>999</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
+    <row r="4" spans="1:55">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -1024,10 +1213,70 @@
       <c r="AI4">
         <v>999</v>
       </c>
+      <c r="AJ4">
+        <v>999</v>
+      </c>
+      <c r="AK4">
+        <v>999</v>
+      </c>
+      <c r="AL4">
+        <v>999</v>
+      </c>
+      <c r="AM4">
+        <v>999</v>
+      </c>
+      <c r="AN4">
+        <v>999</v>
+      </c>
+      <c r="AO4">
+        <v>999</v>
+      </c>
+      <c r="AP4">
+        <v>999</v>
+      </c>
+      <c r="AQ4">
+        <v>999</v>
+      </c>
+      <c r="AR4">
+        <v>999</v>
+      </c>
+      <c r="AS4">
+        <v>999</v>
+      </c>
+      <c r="AT4">
+        <v>999</v>
+      </c>
+      <c r="AU4">
+        <v>999</v>
+      </c>
+      <c r="AV4">
+        <v>999</v>
+      </c>
+      <c r="AW4">
+        <v>999</v>
+      </c>
+      <c r="AX4">
+        <v>999</v>
+      </c>
+      <c r="AY4">
+        <v>999</v>
+      </c>
+      <c r="AZ4">
+        <v>999</v>
+      </c>
+      <c r="BA4">
+        <v>999</v>
+      </c>
+      <c r="BB4">
+        <v>999</v>
+      </c>
+      <c r="BC4">
+        <v>999</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
+    <row r="5" spans="1:55">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -1131,331 +1380,571 @@
       <c r="AI5">
         <v>999</v>
       </c>
+      <c r="AJ5">
+        <v>999</v>
+      </c>
+      <c r="AK5">
+        <v>999</v>
+      </c>
+      <c r="AL5">
+        <v>999</v>
+      </c>
+      <c r="AM5">
+        <v>999</v>
+      </c>
+      <c r="AN5">
+        <v>999</v>
+      </c>
+      <c r="AO5">
+        <v>999</v>
+      </c>
+      <c r="AP5">
+        <v>999</v>
+      </c>
+      <c r="AQ5">
+        <v>999</v>
+      </c>
+      <c r="AR5">
+        <v>999</v>
+      </c>
+      <c r="AS5">
+        <v>999</v>
+      </c>
+      <c r="AT5">
+        <v>999</v>
+      </c>
+      <c r="AU5">
+        <v>999</v>
+      </c>
+      <c r="AV5">
+        <v>999</v>
+      </c>
+      <c r="AW5">
+        <v>999</v>
+      </c>
+      <c r="AX5">
+        <v>999</v>
+      </c>
+      <c r="AY5">
+        <v>999</v>
+      </c>
+      <c r="AZ5">
+        <v>999</v>
+      </c>
+      <c r="BA5">
+        <v>999</v>
+      </c>
+      <c r="BB5">
+        <v>999</v>
+      </c>
+      <c r="BC5">
+        <v>999</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>0</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="6">
+    <row r="6" spans="1:55">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6">
-        <v>0</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="6">
+    <row r="7" spans="1:55">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6">
+    <row r="8" spans="1:55">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
+    <row r="9" spans="1:55">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -1559,10 +2048,70 @@
       <c r="AI9">
         <v>999</v>
       </c>
+      <c r="AJ9">
+        <v>999</v>
+      </c>
+      <c r="AK9">
+        <v>999</v>
+      </c>
+      <c r="AL9">
+        <v>999</v>
+      </c>
+      <c r="AM9">
+        <v>999</v>
+      </c>
+      <c r="AN9">
+        <v>999</v>
+      </c>
+      <c r="AO9">
+        <v>999</v>
+      </c>
+      <c r="AP9">
+        <v>999</v>
+      </c>
+      <c r="AQ9">
+        <v>999</v>
+      </c>
+      <c r="AR9">
+        <v>999</v>
+      </c>
+      <c r="AS9">
+        <v>999</v>
+      </c>
+      <c r="AT9">
+        <v>999</v>
+      </c>
+      <c r="AU9">
+        <v>999</v>
+      </c>
+      <c r="AV9">
+        <v>999</v>
+      </c>
+      <c r="AW9">
+        <v>999</v>
+      </c>
+      <c r="AX9">
+        <v>999</v>
+      </c>
+      <c r="AY9">
+        <v>999</v>
+      </c>
+      <c r="AZ9">
+        <v>999</v>
+      </c>
+      <c r="BA9">
+        <v>999</v>
+      </c>
+      <c r="BB9">
+        <v>999</v>
+      </c>
+      <c r="BC9">
+        <v>999</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>12</v>
+    <row r="10" spans="1:55">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -1666,10 +2215,70 @@
       <c r="AI10">
         <v>999</v>
       </c>
+      <c r="AJ10">
+        <v>999</v>
+      </c>
+      <c r="AK10">
+        <v>999</v>
+      </c>
+      <c r="AL10">
+        <v>999</v>
+      </c>
+      <c r="AM10">
+        <v>999</v>
+      </c>
+      <c r="AN10">
+        <v>999</v>
+      </c>
+      <c r="AO10">
+        <v>999</v>
+      </c>
+      <c r="AP10">
+        <v>999</v>
+      </c>
+      <c r="AQ10">
+        <v>999</v>
+      </c>
+      <c r="AR10">
+        <v>999</v>
+      </c>
+      <c r="AS10">
+        <v>999</v>
+      </c>
+      <c r="AT10">
+        <v>999</v>
+      </c>
+      <c r="AU10">
+        <v>999</v>
+      </c>
+      <c r="AV10">
+        <v>999</v>
+      </c>
+      <c r="AW10">
+        <v>999</v>
+      </c>
+      <c r="AX10">
+        <v>999</v>
+      </c>
+      <c r="AY10">
+        <v>999</v>
+      </c>
+      <c r="AZ10">
+        <v>999</v>
+      </c>
+      <c r="BA10">
+        <v>999</v>
+      </c>
+      <c r="BB10">
+        <v>999</v>
+      </c>
+      <c r="BC10">
+        <v>999</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>13</v>
+    <row r="11" spans="1:55">
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -1773,10 +2382,70 @@
       <c r="AI11">
         <v>999</v>
       </c>
+      <c r="AJ11">
+        <v>999</v>
+      </c>
+      <c r="AK11">
+        <v>999</v>
+      </c>
+      <c r="AL11">
+        <v>999</v>
+      </c>
+      <c r="AM11">
+        <v>999</v>
+      </c>
+      <c r="AN11">
+        <v>999</v>
+      </c>
+      <c r="AO11">
+        <v>999</v>
+      </c>
+      <c r="AP11">
+        <v>999</v>
+      </c>
+      <c r="AQ11">
+        <v>999</v>
+      </c>
+      <c r="AR11">
+        <v>999</v>
+      </c>
+      <c r="AS11">
+        <v>999</v>
+      </c>
+      <c r="AT11">
+        <v>999</v>
+      </c>
+      <c r="AU11">
+        <v>999</v>
+      </c>
+      <c r="AV11">
+        <v>999</v>
+      </c>
+      <c r="AW11">
+        <v>999</v>
+      </c>
+      <c r="AX11">
+        <v>999</v>
+      </c>
+      <c r="AY11">
+        <v>999</v>
+      </c>
+      <c r="AZ11">
+        <v>999</v>
+      </c>
+      <c r="BA11">
+        <v>999</v>
+      </c>
+      <c r="BB11">
+        <v>999</v>
+      </c>
+      <c r="BC11">
+        <v>999</v>
+      </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
+    <row r="12" spans="1:55">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -1880,10 +2549,70 @@
       <c r="AI12">
         <v>999</v>
       </c>
+      <c r="AJ12">
+        <v>999</v>
+      </c>
+      <c r="AK12">
+        <v>999</v>
+      </c>
+      <c r="AL12">
+        <v>999</v>
+      </c>
+      <c r="AM12">
+        <v>999</v>
+      </c>
+      <c r="AN12">
+        <v>999</v>
+      </c>
+      <c r="AO12">
+        <v>999</v>
+      </c>
+      <c r="AP12">
+        <v>999</v>
+      </c>
+      <c r="AQ12">
+        <v>999</v>
+      </c>
+      <c r="AR12">
+        <v>999</v>
+      </c>
+      <c r="AS12">
+        <v>999</v>
+      </c>
+      <c r="AT12">
+        <v>999</v>
+      </c>
+      <c r="AU12">
+        <v>999</v>
+      </c>
+      <c r="AV12">
+        <v>999</v>
+      </c>
+      <c r="AW12">
+        <v>999</v>
+      </c>
+      <c r="AX12">
+        <v>999</v>
+      </c>
+      <c r="AY12">
+        <v>999</v>
+      </c>
+      <c r="AZ12">
+        <v>999</v>
+      </c>
+      <c r="BA12">
+        <v>999</v>
+      </c>
+      <c r="BB12">
+        <v>999</v>
+      </c>
+      <c r="BC12">
+        <v>999</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>15</v>
+    <row r="13" spans="1:55">
+      <c r="A13" t="s">
+        <v>27</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -1987,10 +2716,70 @@
       <c r="AI13">
         <v>999</v>
       </c>
+      <c r="AJ13">
+        <v>999</v>
+      </c>
+      <c r="AK13">
+        <v>999</v>
+      </c>
+      <c r="AL13">
+        <v>999</v>
+      </c>
+      <c r="AM13">
+        <v>999</v>
+      </c>
+      <c r="AN13">
+        <v>999</v>
+      </c>
+      <c r="AO13">
+        <v>999</v>
+      </c>
+      <c r="AP13">
+        <v>999</v>
+      </c>
+      <c r="AQ13">
+        <v>999</v>
+      </c>
+      <c r="AR13">
+        <v>999</v>
+      </c>
+      <c r="AS13">
+        <v>999</v>
+      </c>
+      <c r="AT13">
+        <v>999</v>
+      </c>
+      <c r="AU13">
+        <v>999</v>
+      </c>
+      <c r="AV13">
+        <v>999</v>
+      </c>
+      <c r="AW13">
+        <v>999</v>
+      </c>
+      <c r="AX13">
+        <v>999</v>
+      </c>
+      <c r="AY13">
+        <v>999</v>
+      </c>
+      <c r="AZ13">
+        <v>999</v>
+      </c>
+      <c r="BA13">
+        <v>999</v>
+      </c>
+      <c r="BB13">
+        <v>999</v>
+      </c>
+      <c r="BC13">
+        <v>999</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>16</v>
+    <row r="14" spans="1:55">
+      <c r="A14" t="s">
+        <v>28</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -2094,224 +2883,404 @@
       <c r="AI14">
         <v>999</v>
       </c>
+      <c r="AJ14">
+        <v>999</v>
+      </c>
+      <c r="AK14">
+        <v>999</v>
+      </c>
+      <c r="AL14">
+        <v>999</v>
+      </c>
+      <c r="AM14">
+        <v>999</v>
+      </c>
+      <c r="AN14">
+        <v>999</v>
+      </c>
+      <c r="AO14">
+        <v>999</v>
+      </c>
+      <c r="AP14">
+        <v>999</v>
+      </c>
+      <c r="AQ14">
+        <v>999</v>
+      </c>
+      <c r="AR14">
+        <v>999</v>
+      </c>
+      <c r="AS14">
+        <v>999</v>
+      </c>
+      <c r="AT14">
+        <v>999</v>
+      </c>
+      <c r="AU14">
+        <v>999</v>
+      </c>
+      <c r="AV14">
+        <v>999</v>
+      </c>
+      <c r="AW14">
+        <v>999</v>
+      </c>
+      <c r="AX14">
+        <v>999</v>
+      </c>
+      <c r="AY14">
+        <v>999</v>
+      </c>
+      <c r="AZ14">
+        <v>999</v>
+      </c>
+      <c r="BA14">
+        <v>999</v>
+      </c>
+      <c r="BB14">
+        <v>999</v>
+      </c>
+      <c r="BC14">
+        <v>999</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="6">
+    <row r="15" spans="1:55">
+      <c r="A15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>0</v>
-      </c>
-      <c r="W16" s="6">
-        <v>0</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="6">
+    <row r="16" spans="1:55">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>19</v>
+    <row r="17" spans="1:55">
+      <c r="A17" t="s">
+        <v>31</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -2415,10 +3384,70 @@
       <c r="AI17">
         <v>999</v>
       </c>
+      <c r="AJ17">
+        <v>999</v>
+      </c>
+      <c r="AK17">
+        <v>999</v>
+      </c>
+      <c r="AL17">
+        <v>999</v>
+      </c>
+      <c r="AM17">
+        <v>999</v>
+      </c>
+      <c r="AN17">
+        <v>999</v>
+      </c>
+      <c r="AO17">
+        <v>999</v>
+      </c>
+      <c r="AP17">
+        <v>999</v>
+      </c>
+      <c r="AQ17">
+        <v>999</v>
+      </c>
+      <c r="AR17">
+        <v>999</v>
+      </c>
+      <c r="AS17">
+        <v>999</v>
+      </c>
+      <c r="AT17">
+        <v>999</v>
+      </c>
+      <c r="AU17">
+        <v>999</v>
+      </c>
+      <c r="AV17">
+        <v>999</v>
+      </c>
+      <c r="AW17">
+        <v>999</v>
+      </c>
+      <c r="AX17">
+        <v>999</v>
+      </c>
+      <c r="AY17">
+        <v>999</v>
+      </c>
+      <c r="AZ17">
+        <v>999</v>
+      </c>
+      <c r="BA17">
+        <v>999</v>
+      </c>
+      <c r="BB17">
+        <v>999</v>
+      </c>
+      <c r="BC17">
+        <v>999</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
+    <row r="18" spans="1:55">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -2522,10 +3551,70 @@
       <c r="AI18">
         <v>999</v>
       </c>
+      <c r="AJ18">
+        <v>999</v>
+      </c>
+      <c r="AK18">
+        <v>999</v>
+      </c>
+      <c r="AL18">
+        <v>999</v>
+      </c>
+      <c r="AM18">
+        <v>999</v>
+      </c>
+      <c r="AN18">
+        <v>999</v>
+      </c>
+      <c r="AO18">
+        <v>999</v>
+      </c>
+      <c r="AP18">
+        <v>999</v>
+      </c>
+      <c r="AQ18">
+        <v>999</v>
+      </c>
+      <c r="AR18">
+        <v>999</v>
+      </c>
+      <c r="AS18">
+        <v>999</v>
+      </c>
+      <c r="AT18">
+        <v>999</v>
+      </c>
+      <c r="AU18">
+        <v>999</v>
+      </c>
+      <c r="AV18">
+        <v>999</v>
+      </c>
+      <c r="AW18">
+        <v>999</v>
+      </c>
+      <c r="AX18">
+        <v>999</v>
+      </c>
+      <c r="AY18">
+        <v>999</v>
+      </c>
+      <c r="AZ18">
+        <v>999</v>
+      </c>
+      <c r="BA18">
+        <v>999</v>
+      </c>
+      <c r="BB18">
+        <v>999</v>
+      </c>
+      <c r="BC18">
+        <v>999</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>21</v>
+    <row r="19" spans="1:55">
+      <c r="A19" t="s">
+        <v>33</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -2629,10 +3718,70 @@
       <c r="AI19">
         <v>999</v>
       </c>
+      <c r="AJ19">
+        <v>999</v>
+      </c>
+      <c r="AK19">
+        <v>999</v>
+      </c>
+      <c r="AL19">
+        <v>999</v>
+      </c>
+      <c r="AM19">
+        <v>999</v>
+      </c>
+      <c r="AN19">
+        <v>999</v>
+      </c>
+      <c r="AO19">
+        <v>999</v>
+      </c>
+      <c r="AP19">
+        <v>999</v>
+      </c>
+      <c r="AQ19">
+        <v>999</v>
+      </c>
+      <c r="AR19">
+        <v>999</v>
+      </c>
+      <c r="AS19">
+        <v>999</v>
+      </c>
+      <c r="AT19">
+        <v>999</v>
+      </c>
+      <c r="AU19">
+        <v>999</v>
+      </c>
+      <c r="AV19">
+        <v>999</v>
+      </c>
+      <c r="AW19">
+        <v>999</v>
+      </c>
+      <c r="AX19">
+        <v>999</v>
+      </c>
+      <c r="AY19">
+        <v>999</v>
+      </c>
+      <c r="AZ19">
+        <v>999</v>
+      </c>
+      <c r="BA19">
+        <v>999</v>
+      </c>
+      <c r="BB19">
+        <v>999</v>
+      </c>
+      <c r="BC19">
+        <v>999</v>
+      </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>22</v>
+    <row r="20" spans="1:55">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -2736,10 +3885,70 @@
       <c r="AI20">
         <v>999</v>
       </c>
+      <c r="AJ20">
+        <v>999</v>
+      </c>
+      <c r="AK20">
+        <v>999</v>
+      </c>
+      <c r="AL20">
+        <v>999</v>
+      </c>
+      <c r="AM20">
+        <v>999</v>
+      </c>
+      <c r="AN20">
+        <v>999</v>
+      </c>
+      <c r="AO20">
+        <v>999</v>
+      </c>
+      <c r="AP20">
+        <v>999</v>
+      </c>
+      <c r="AQ20">
+        <v>999</v>
+      </c>
+      <c r="AR20">
+        <v>999</v>
+      </c>
+      <c r="AS20">
+        <v>999</v>
+      </c>
+      <c r="AT20">
+        <v>999</v>
+      </c>
+      <c r="AU20">
+        <v>999</v>
+      </c>
+      <c r="AV20">
+        <v>999</v>
+      </c>
+      <c r="AW20">
+        <v>999</v>
+      </c>
+      <c r="AX20">
+        <v>999</v>
+      </c>
+      <c r="AY20">
+        <v>999</v>
+      </c>
+      <c r="AZ20">
+        <v>999</v>
+      </c>
+      <c r="BA20">
+        <v>999</v>
+      </c>
+      <c r="BB20">
+        <v>999</v>
+      </c>
+      <c r="BC20">
+        <v>999</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>23</v>
+    <row r="21" spans="1:55">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -2843,10 +4052,70 @@
       <c r="AI21">
         <v>999</v>
       </c>
+      <c r="AJ21">
+        <v>999</v>
+      </c>
+      <c r="AK21">
+        <v>999</v>
+      </c>
+      <c r="AL21">
+        <v>999</v>
+      </c>
+      <c r="AM21">
+        <v>999</v>
+      </c>
+      <c r="AN21">
+        <v>999</v>
+      </c>
+      <c r="AO21">
+        <v>999</v>
+      </c>
+      <c r="AP21">
+        <v>999</v>
+      </c>
+      <c r="AQ21">
+        <v>999</v>
+      </c>
+      <c r="AR21">
+        <v>999</v>
+      </c>
+      <c r="AS21">
+        <v>999</v>
+      </c>
+      <c r="AT21">
+        <v>999</v>
+      </c>
+      <c r="AU21">
+        <v>999</v>
+      </c>
+      <c r="AV21">
+        <v>999</v>
+      </c>
+      <c r="AW21">
+        <v>999</v>
+      </c>
+      <c r="AX21">
+        <v>999</v>
+      </c>
+      <c r="AY21">
+        <v>999</v>
+      </c>
+      <c r="AZ21">
+        <v>999</v>
+      </c>
+      <c r="BA21">
+        <v>999</v>
+      </c>
+      <c r="BB21">
+        <v>999</v>
+      </c>
+      <c r="BC21">
+        <v>999</v>
+      </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>24</v>
+    <row r="22" spans="1:55">
+      <c r="A22" t="s">
+        <v>36</v>
       </c>
       <c r="B22">
         <v>999</v>
@@ -2948,10 +4217,241 @@
         <v>999</v>
       </c>
       <c r="AI22">
+        <v>999</v>
+      </c>
+      <c r="AJ22">
+        <v>999</v>
+      </c>
+      <c r="AK22">
+        <v>999</v>
+      </c>
+      <c r="AL22">
+        <v>999</v>
+      </c>
+      <c r="AM22">
+        <v>999</v>
+      </c>
+      <c r="AN22">
+        <v>999</v>
+      </c>
+      <c r="AO22">
+        <v>999</v>
+      </c>
+      <c r="AP22">
+        <v>999</v>
+      </c>
+      <c r="AQ22">
+        <v>999</v>
+      </c>
+      <c r="AR22">
+        <v>999</v>
+      </c>
+      <c r="AS22">
+        <v>999</v>
+      </c>
+      <c r="AT22">
+        <v>999</v>
+      </c>
+      <c r="AU22">
+        <v>999</v>
+      </c>
+      <c r="AV22">
+        <v>999</v>
+      </c>
+      <c r="AW22">
+        <v>999</v>
+      </c>
+      <c r="AX22">
+        <v>999</v>
+      </c>
+      <c r="AY22">
+        <v>999</v>
+      </c>
+      <c r="AZ22">
+        <v>999</v>
+      </c>
+      <c r="BA22">
+        <v>999</v>
+      </c>
+      <c r="BB22">
+        <v>999</v>
+      </c>
+      <c r="BC22">
         <v>999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42897752-8724-4E2F-BDF1-215A481562F1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FC48B54-3A5C-4FB2-9D75-1ED303C9FFAC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56C72FE-EE37-4DCD-B289-D0075B4E86E6}"/>
 </file>